--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E5C60B-4950-4087-8802-EE23AFCAE01C}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9790ADE8-DDF2-48B2-9B68-0CA719996490}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Produto</t>
   </si>
@@ -42,16 +42,10 @@
     <t>Familia</t>
   </si>
   <si>
-    <t>NEW BASE VITÓRIA WZ</t>
-  </si>
-  <si>
     <t>BASE SHANGHAI PU 1.05 CASTANHO</t>
   </si>
   <si>
     <t>BASE SHANGHAI</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1 BEGE</t>
   </si>
 </sst>
 </file>
@@ -403,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B43164-A157-422F-BA0D-8470CD7BA9D2}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -432,36 +426,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>9295</v>
+        <v>16904</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>14053</v>
+        <v>21633</v>
       </c>
       <c r="D2">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>16904</v>
-      </c>
-      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3">
-        <v>21633</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9790ADE8-DDF2-48B2-9B68-0CA719996490}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B0D3E-F307-48AD-9872-85EFAEFD5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Produto</t>
   </si>
@@ -46,6 +46,12 @@
   </si>
   <si>
     <t>BASE SHANGHAI</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ 1.1  BEGE 435</t>
+  </si>
+  <si>
+    <t>NEW BASE VITÓRIA WZ</t>
   </si>
 </sst>
 </file>
@@ -397,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B43164-A157-422F-BA0D-8470CD7BA9D2}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -441,6 +447,23 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>9295</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>14053</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B0D3E-F307-48AD-9872-85EFAEFD5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178CC6B-7AEB-4F4C-9BD5-4C88E264C694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Produto</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>BASE SHANGHAI</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ 1.1  BEGE 435</t>
-  </si>
-  <si>
-    <t>NEW BASE VITÓRIA WZ</t>
   </si>
 </sst>
 </file>
@@ -403,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B43164-A157-422F-BA0D-8470CD7BA9D2}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -447,23 +441,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>9295</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>14053</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\SMART-STOCK\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178CC6B-7AEB-4F4C-9BD5-4C88E264C694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D178CC6B-7AEB-4F4C-9BD5-4C88E264C694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E1DE391-D6E4-4F43-A51B-CCF00FC4CEAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Produto</t>
   </si>
@@ -40,12 +40,6 @@
   </si>
   <si>
     <t>Familia</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI PU 1.05 CASTANHO</t>
-  </si>
-  <si>
-    <t>BASE SHANGHAI</t>
   </si>
 </sst>
 </file>
@@ -397,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B43164-A157-422F-BA0D-8470CD7BA9D2}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -424,23 +418,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>16904</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>21633</v>
-      </c>
-      <c r="D2">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
